--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.7175600459398</v>
+        <v>7.916603507465218</v>
       </c>
       <c r="D2" t="n">
-        <v>49.11655106757426</v>
+        <v>7.981439548480817</v>
       </c>
       <c r="E2" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F2" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.73046231897716</v>
+        <v>9.706200126833789</v>
       </c>
       <c r="D3" t="n">
-        <v>60.06580285537633</v>
+        <v>9.760692963998654</v>
       </c>
       <c r="E3" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F3" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.88692553377903</v>
+        <v>3.719125399239093</v>
       </c>
       <c r="D4" t="n">
-        <v>23.10263236267781</v>
+        <v>3.754177758935144</v>
       </c>
       <c r="E4" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F4" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.92405497005684</v>
+        <v>1.775158932634236</v>
       </c>
       <c r="D5" t="n">
-        <v>11.0281914051297</v>
+        <v>1.792081103333576</v>
       </c>
       <c r="E5" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F5" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.783229071841404</v>
+        <v>1.427274724174228</v>
       </c>
       <c r="D6" t="n">
-        <v>5.826677036527364</v>
+        <v>0.9468350184356967</v>
       </c>
       <c r="E6" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F6" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.77976847121693</v>
+        <v>6.139212376572752</v>
       </c>
       <c r="D7" t="n">
-        <v>37.85496520794067</v>
+        <v>6.151431846290359</v>
       </c>
       <c r="E7" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F7" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.05398818948011</v>
+        <v>3.583773080790518</v>
       </c>
       <c r="D8" t="n">
-        <v>9.100072246520618</v>
+        <v>1.4787617400596</v>
       </c>
       <c r="E8" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F8" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67317782926645</v>
+        <v>10.6718913972558</v>
       </c>
       <c r="D9" t="n">
-        <v>65.70628364768073</v>
+        <v>10.67727109274812</v>
       </c>
       <c r="E9" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F9" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>63.0698400943009</v>
+        <v>10.2488490153239</v>
       </c>
       <c r="D10" t="n">
-        <v>63.11123797761122</v>
+        <v>10.25557617136182</v>
       </c>
       <c r="E10" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F10" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>58.34667043300143</v>
+        <v>9.481333945362733</v>
       </c>
       <c r="D11" t="n">
-        <v>38.95485425117907</v>
+        <v>6.330163815816599</v>
       </c>
       <c r="E11" t="n">
-        <v>21.05361370276998</v>
+        <v>3.421212226700121</v>
       </c>
       <c r="F11" t="n">
-        <v>21.91651118091961</v>
+        <v>3.561433066899438</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
